--- a/London_Finance_Prospect_List.xlsx
+++ b/London_Finance_Prospect_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$S$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$U$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S221"/>
+  <dimension ref="A1:U221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -486,6 +502,8 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -584,6 +602,16 @@
           <t>Brand Preference</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Country Confidence</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Country Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -612,7 +640,7 @@
           <t>hazem.eltaha@hsbc.co.uk</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -633,6 +661,16 @@
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>London conference activity; no explicit LinkedIn location</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -661,7 +699,7 @@
           <t>laura.morgante@hsbc.com</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -682,6 +720,16 @@
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -710,9 +758,9 @@
           <t>andreas.fenneker@hsbc.de</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -731,6 +779,16 @@
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>based in Dusseldorf, Germany; HSBC Germany, Associate Director Marketing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -759,7 +817,7 @@
           <t>steve.thomas@hsbc.com</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -780,6 +838,16 @@
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in London</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -808,7 +876,7 @@
           <t>nicole.german@hsbc.com</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -829,6 +897,16 @@
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>HSBC CIB (London-based team); no explicit location</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -857,7 +935,7 @@
           <t>alex.leay@hsbc.com</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -878,6 +956,16 @@
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Head of UK Marketing, HSBC Asset Management</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -906,7 +994,7 @@
           <t>william.barraclough@hsbc.com</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -927,6 +1015,16 @@
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>profile: located in United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -955,7 +1053,7 @@
           <t>ben.harding@barclays.com</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -976,6 +1074,16 @@
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; Barclays UK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1004,7 +1112,7 @@
           <t>dolika.dhar@barclays.com</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1025,6 +1133,16 @@
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/dolika-dhar; VP Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1053,7 +1171,7 @@
           <t>Fred.doyhamboure@barclays.com</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1074,6 +1192,16 @@
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/fred-doyhamboure; Markets Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1102,7 +1230,7 @@
           <t>amit.singh@barclays.com</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1123,6 +1251,16 @@
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>TheOrg Barclays Corporate Banking; exact title match, London-based role</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1151,7 +1289,7 @@
           <t>magnus.deuling@barclays.com</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1172,6 +1310,16 @@
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>profile matched (MarketsOne, Barclays IB) but no explicit location</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1200,7 +1348,7 @@
           <t>lauren.stewart@barclays.com</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1221,6 +1369,16 @@
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; Barclays UK</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1249,7 +1407,7 @@
           <t>priya.mallinson@barclays.com</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1270,6 +1428,16 @@
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/priyamallinson; exact title match</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1298,7 +1466,7 @@
           <t>eleanor.whittaker@natwest.com</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1319,6 +1487,16 @@
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in London</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1347,7 +1525,7 @@
           <t>maria.lagutina@natwest.com</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1368,6 +1546,16 @@
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/marialagutina; based in London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1396,7 +1584,7 @@
           <t>wendy.redshaw@natwest.com</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1417,6 +1605,16 @@
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>NatWest Retail CDIO, London-based; London Tech Week speaker</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1445,7 +1643,7 @@
           <t>robyn.johnston@natwest.com</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1466,6 +1664,16 @@
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in London (CIB Marketing)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1494,7 +1702,7 @@
           <t>marty.carroll@natwest.com</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1515,6 +1723,16 @@
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1543,7 +1761,7 @@
           <t>Dasha.lukiniha@natwest.com</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1564,6 +1782,16 @@
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in London</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1592,7 +1820,7 @@
           <t>nicky.mackrell@natwest.com</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1613,6 +1841,16 @@
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com; based in London</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1641,7 +1879,7 @@
           <t>matthew.harwood@natwest.com</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1662,6 +1900,16 @@
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>profile: located in United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1690,7 +1938,7 @@
           <t>kate.litler@natwest.com</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1711,6 +1959,16 @@
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>30-yr NatWest/RBS UK career; UK-based</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1739,7 +1997,7 @@
           <t>grant.thomas@natwest.com</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1760,6 +2018,16 @@
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>profile: London Area, United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1788,7 +2056,7 @@
           <t>tanvi.gokhale@natwest.com</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1809,6 +2077,16 @@
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com; based in London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1837,7 +2115,7 @@
           <t>amanda.scott@natwest.com</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1858,6 +2136,16 @@
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; NatWest UK</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1886,7 +2174,7 @@
           <t>aimee-munro.hood@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1907,6 +2195,16 @@
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; Lloyds is UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1935,7 +2233,7 @@
           <t>laurie.hodge@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -1956,6 +2254,16 @@
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; Lloyds is UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1984,7 +2292,7 @@
           <t>jay.sadfar@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -2005,6 +2313,16 @@
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>not searched individually; Lloyds is UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2033,7 +2351,7 @@
           <t>ben.logan@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -2054,6 +2372,16 @@
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>ambiguous profile; Lloyds is UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2082,7 +2410,7 @@
           <t>seena.samani@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -2103,6 +2431,16 @@
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/seena-s; Head of Marketing Effectiveness</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2131,7 +2469,7 @@
           <t>ella.davis@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -2152,6 +2490,16 @@
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/ella-davis; Lloyds</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2180,7 +2528,7 @@
           <t>sangeetha.narasimhan1@lloydsbanking.com</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -2201,6 +2549,16 @@
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/sangeethacn; UK Companies House officer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2229,7 +2587,7 @@
           <t>idoia.muguruza@gruposantander.com</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2250,6 +2608,16 @@
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Madrid Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2278,7 +2646,7 @@
           <t>antonio.herranz@gruposantander.es</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2299,6 +2667,16 @@
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2327,7 +2705,7 @@
           <t>bernabe.mohedano@gruposantander.es</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2348,6 +2726,16 @@
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>es.linkedin.com; Madrid; Santander Espana</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2376,7 +2764,7 @@
           <t>Ana.Donaire@gruposantander.es</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2397,6 +2785,16 @@
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain; Head of Brand &amp; Corporate Marketing</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2425,7 +2823,7 @@
           <t>silviamerino@gruposantander.com</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2446,6 +2844,16 @@
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain; Santander CIB</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2474,7 +2882,7 @@
           <t>andmoran@gruposantander.com</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2495,6 +2903,16 @@
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>es.linkedin.com; Spain-based, Banco Santander</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2523,7 +2941,7 @@
           <t>jorge.varela@gruposantander.com</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2544,6 +2962,16 @@
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2572,7 +3000,7 @@
           <t>david.meza@gruposantander.com</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2593,6 +3021,16 @@
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; Santander Spain AI role</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2621,7 +3059,7 @@
           <t>adam.beardmore@gruposantander.com</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2642,6 +3080,16 @@
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; HQ default (may be UK - unverified)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2670,7 +3118,7 @@
           <t>luis.calleja3@bbva.com</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2691,6 +3139,16 @@
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2719,7 +3177,7 @@
           <t>miguel.alcala@bbva.com</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2740,6 +3198,16 @@
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain; BBVA Spark Spain since 2022</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2768,7 +3236,7 @@
           <t>horacio.ballestrin@bbva.com</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2789,6 +3257,16 @@
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>profile: based in Spain (ex-BBVA Mexico)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2817,7 +3295,7 @@
           <t>david.arconada@bbva.com</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2838,6 +3316,16 @@
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>profile: Boadilla del Monte, Madrid (BBVA HQ)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2866,7 +3354,7 @@
           <t>elsa.moya@grupobbva.com</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2887,6 +3375,16 @@
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>es.linkedin.com/in/elsa-moya-garcia; directora BBVA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2915,7 +3413,7 @@
           <t>ignacio.gomez@bbva.com</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2936,6 +3434,16 @@
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Madrid Metropolitan Area; BBVA CIB</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2964,7 +3472,7 @@
           <t>sofia.rodriguez-sahagun@bbva.com</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2985,6 +3493,16 @@
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Madrid Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3013,7 +3531,7 @@
           <t>oscar.moya@bbva.com</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -3034,6 +3552,16 @@
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain (Oscar Moya Gomez)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3062,7 +3590,7 @@
           <t>ramon.calderon@bbva.com</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -3083,6 +3611,16 @@
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>es.linkedin; Head Digital Sales &amp; Marketing BBVA Spain</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3111,9 +3649,9 @@
           <t>walter.rizzi@bbva.com</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Spain</t>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3132,6 +3670,16 @@
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>Milan, Italy; Country Manager BBVA Italy (NOTE: outside user 6-country list)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3160,7 +3708,7 @@
           <t>alfonso.fernandez.iglesias@bbva.com</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -3181,6 +3729,16 @@
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Madrid Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3209,9 +3767,9 @@
           <t>Martin.Eizaga@bbva.com</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Spain</t>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3230,6 +3788,16 @@
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>CMO/Head of Product BBVA Digital Banking Italy; likely Italy, some es.linkedin activity (may be Madrid-based)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3258,9 +3826,9 @@
           <t>nicola.cecchetto@bbva.com</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Spain</t>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3279,6 +3847,16 @@
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>Milan, Italy; Head of Legal BBVA Italy (NOTE: outside user 6-country list)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3307,7 +3885,7 @@
           <t>cogez.damien@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3328,6 +3906,16 @@
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris, France</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3356,7 +3944,7 @@
           <t>tutku.salihoglu@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3377,6 +3965,16 @@
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>fr.linkedin.com; BNP Paribas Cardif (Paris)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3405,7 +4003,7 @@
           <t>mitra.moinfar@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3426,6 +4024,16 @@
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris; leads Mobile Journey team</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3454,7 +4062,7 @@
           <t>romain.rossetti@bnpparibas-am.com</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3475,6 +4083,16 @@
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Paris Metropolitan Region</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3503,9 +4121,9 @@
           <t>lisa.bush@bnpparibas-am.com</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3524,6 +4142,16 @@
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB; BNP Paribas AM Northern Europe</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3552,7 +4180,7 @@
           <t>Atman.bentahar@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3573,6 +4201,16 @@
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>fr.linkedin.com; BNP Paribas Omnichannel</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3601,7 +4239,7 @@
           <t>bachiri.soufiane@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3622,6 +4260,16 @@
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>profile: Neuilly-sur-Seine (Paris)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3650,7 +4298,7 @@
           <t>charlotte.cren@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3671,6 +4319,16 @@
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris, France</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3699,7 +4357,7 @@
           <t>deborrah.flament@bnpparibas.com</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3720,6 +4378,16 @@
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Paris Metropolitan Region</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3748,7 +4416,7 @@
           <t>onsi.kahlaoui@sgcib.com</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3769,6 +4437,16 @@
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>profile: Suresnes (Paris area)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3797,7 +4475,7 @@
           <t>giorgio.bellati@socgen.com</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3818,6 +4496,16 @@
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Paris Metropolitan Region</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3846,7 +4534,7 @@
           <t>Pierre-Emmanuel.fraisse@socgen.com</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3867,6 +4555,16 @@
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>profile: Villeneuve-d'Ascq, France</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3895,7 +4593,7 @@
           <t>tiphaine.massard-godard@socgen.com</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3916,6 +4614,16 @@
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Paris Metropolitan Region</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3944,7 +4652,7 @@
           <t>Salma.radi@socgen.com</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -3965,6 +4673,16 @@
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris; SGCIB</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3993,7 +4711,7 @@
           <t>laetitia.bianchi@sgcib.com</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4014,6 +4732,16 @@
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris, FR; SGCIB Global Markets</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4042,7 +4770,7 @@
           <t>stephanie.vicat@credit-agricole-sa.fr</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4063,6 +4791,16 @@
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>fr.linkedin; Groupe Credit Agricole (France)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4091,7 +4829,7 @@
           <t>shivanisunil.bhagat@ca-cib.com</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4112,6 +4850,16 @@
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>fr.linkedin; CA CIB / CACEIS (Paris)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4140,7 +4888,7 @@
           <t>jprovost@ca-cf.fr</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4161,6 +4909,16 @@
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>fr.linkedin; CA Consumer Finance, Paris</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4189,7 +4947,7 @@
           <t>marie.schouvey@ca-cib.com</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4210,6 +4968,16 @@
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>profile: Le Mesnil-Saint-Denis (Paris region)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4238,7 +5006,7 @@
           <t>nicolas.renaut@credit-agricole-sa.fr</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4259,6 +5027,16 @@
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris; Credit Agricole SA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4287,7 +5065,7 @@
           <t>vincent.giraudel@credit-agricole-sa.fr</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4308,6 +5086,16 @@
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>profile: Montrouge (CA SA HQ); now CA Ile-de-France</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4336,7 +5124,7 @@
           <t>y.arkat@ca-cib.com</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4357,6 +5145,16 @@
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Paris Metropolitan Region</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4385,9 +5183,9 @@
           <t>julian.nastase@ca-cib.com</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4406,6 +5204,16 @@
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/iuliann; Business Manager CA-CIB London</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4434,7 +5242,7 @@
           <t>james.hanscombe@ca-cib.com</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>France</t>
         </is>
@@ -4455,6 +5263,16 @@
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; likely CA-CIB London/UK - UNCONFIRMED, retry</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4483,7 +5301,7 @@
           <t>adis.tutundzic@ing.com</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4504,6 +5322,16 @@
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>profile: Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4532,7 +5360,7 @@
           <t>michel.drupsteen@ing.com</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4553,6 +5381,16 @@
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam, NL</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4581,7 +5419,7 @@
           <t>yvon.martin@ing.com</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4602,6 +5440,16 @@
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam (was ING France, now global brand in NL)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4630,7 +5478,7 @@
           <t>arjen.hoekstra@ing.com</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4651,6 +5499,16 @@
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>nl.linkedin.com/in/aohoekstra; ING Business Banking NL</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4679,7 +5537,7 @@
           <t>willem.speelman@ing.com</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4700,6 +5558,16 @@
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam, Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4728,7 +5596,7 @@
           <t>amit.vats@ing.com</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4749,6 +5617,16 @@
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; ING NL role, @ing.com</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4777,7 +5655,7 @@
           <t>robert.rugebregt@ing.com</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4798,6 +5676,16 @@
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>no clean profile match; ING (NL)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4826,7 +5714,7 @@
           <t>omer.cerrahoglu@ing.com</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4847,6 +5735,16 @@
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam, Netherlands; ING NL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4875,7 +5773,7 @@
           <t>jaap.burggraaff@ing.com</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4896,6 +5794,16 @@
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>profile: Geldermalsen, Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4924,7 +5832,7 @@
           <t>niels.stroeve@ing.com</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4945,6 +5853,16 @@
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>nl.linkedin.com/in/stroeve; Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4973,7 +5891,7 @@
           <t>aksidan.kukalev@ing.com</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -4994,6 +5912,16 @@
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); ING NL HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5022,7 +5950,7 @@
           <t>murat.ayrancioglu@ing.com</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5043,6 +5971,16 @@
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); ING NL HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5071,7 +6009,7 @@
           <t>arjen.noordeman@ing.com</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5092,6 +6030,16 @@
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam, Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5120,7 +6068,7 @@
           <t>marijke.goudberg@nl.abnamro.com</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5141,6 +6089,16 @@
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>profile: Leiden, Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5169,7 +6127,7 @@
           <t>benko.vermolen@nl.abnamro.com</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5190,6 +6148,16 @@
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>no clean LinkedIn match; Dutch (NL running/social profiles)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5218,7 +6186,7 @@
           <t>yorick.naeff@nl.abnamro.com</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5239,6 +6207,16 @@
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam; Head of Innovation ABN AMRO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5267,7 +6245,7 @@
           <t>lisa.dubach@nl.abnamro.com</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5288,6 +6266,16 @@
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam, NH, NL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5316,7 +6304,7 @@
           <t>erik.wijnen@nl.abnamro.com</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
@@ -5337,6 +6325,16 @@
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>profile: Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5365,9 +6363,9 @@
           <t>aude.josset@fr.abnamro.com</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>France</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5386,6 +6384,16 @@
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris, FR; ABN AMRO Investment Solutions</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5414,7 +6422,7 @@
           <t>joao.forjaztrigueiros@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5435,6 +6443,16 @@
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>profile: Lisbon</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5463,7 +6481,7 @@
           <t>andrecorreia@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5484,6 +6502,16 @@
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>profile: Lisbon, PT</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5512,7 +6540,7 @@
           <t>rachel.ferreira@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5533,6 +6561,16 @@
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; BCP is Portugal-domestic</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5561,7 +6599,7 @@
           <t>isantos@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5582,6 +6620,16 @@
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>pt.linkedin; Lisbon, PT</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5610,7 +6658,7 @@
           <t>fmarques@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5631,6 +6679,16 @@
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>profile: Lisbon, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5659,7 +6717,7 @@
           <t>fernanda.aguiar@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5680,6 +6738,16 @@
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>pt.linkedin; Lisbon Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5708,7 +6776,7 @@
           <t>jose.nunes@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5729,6 +6797,16 @@
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>profile: Oeiras (Lisbon area)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5757,7 +6835,7 @@
           <t>pedromendes@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5778,6 +6856,16 @@
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>profile: Lisbon</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5806,7 +6894,7 @@
           <t>miguel.almeida@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5827,6 +6915,16 @@
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>no explicit location; Millennium BCP Portugal team</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5855,7 +6953,7 @@
           <t>pedro.beija@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5876,6 +6974,16 @@
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>pt.linkedin; Lisbon, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5904,7 +7012,7 @@
           <t>joao.jesus@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5925,6 +7033,16 @@
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>BCP DATO (Lisbon); no explicit location on profile</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5953,7 +7071,7 @@
           <t>jose.farinha@millenniumbcp.pt</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5974,6 +7092,16 @@
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; BCP is Portugal-domestic</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6002,9 +7130,9 @@
           <t>sam.pandya@db.com</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6023,6 +7151,16 @@
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/sampandya; DB</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6051,9 +7189,9 @@
           <t>stephen.bell@db.com</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
@@ -6072,6 +7210,16 @@
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>MD Global Head FIC/Securities Svcs Ops; ex-JPM EMEA London - likely London, unconfirmed</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6100,7 +7248,7 @@
           <t>marcel.everts@db.com</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6121,6 +7269,16 @@
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>no explicit location; HQ default (Dutch name - could be NL)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6149,9 +7307,9 @@
           <t>raquel.carrillo@db.com</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -6170,6 +7328,16 @@
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid; DB Espana Head of Marketing</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6198,9 +7366,9 @@
           <t>Nicki.saini@db.com</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -6219,6 +7387,16 @@
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>DB Event &amp; Partnership Marketing team is London-based; unconfirmed</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6247,7 +7425,7 @@
           <t>brigitte.koetting@db.com</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6268,6 +7446,16 @@
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>profile: Hesse, Germany (Frankfurt)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6296,7 +7484,7 @@
           <t>merle.meier-holsten@db.com</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6317,6 +7505,16 @@
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>profile: Frankfurt, Germany</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6345,7 +7543,7 @@
           <t>priyanka.dayal@db.com</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6366,6 +7564,16 @@
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>no clean location; DB Global Marketing (HQ default)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6394,7 +7602,7 @@
           <t>kim-maria.kranz@db.com</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6415,6 +7623,16 @@
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>profile: Munich, Germany</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6443,7 +7661,7 @@
           <t>holger.fischer@db.com</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6464,6 +7682,16 @@
         </is>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; DB Brand Strategy (de)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6492,7 +7720,7 @@
           <t>mina.saidze@db.com</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6513,6 +7741,16 @@
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>profile: Germany (Berlin)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6541,7 +7779,7 @@
           <t>david.dommel@db.com</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6562,6 +7800,16 @@
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>profile: Berlin; DB Head of Performance Marketing</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6586,7 +7834,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6607,6 +7855,16 @@
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>no email/no clean match; DB (HQ default)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6635,9 +7893,9 @@
           <t>Morgane.constanty@db.com</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6656,6 +7914,16 @@
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>speaks at London fintech events; DB AI/Corporate Bank - likely London, unconfirmed</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6684,7 +7952,7 @@
           <t>marcin.belinski@db.com</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -6705,6 +7973,16 @@
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>de.linkedin.com/in/marcin-belinski; DB Product Leader</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6733,7 +8011,7 @@
           <t>caznar@caixabankpc.com</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6754,6 +8032,16 @@
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; CaixaBank (Barcelona)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6782,7 +8070,7 @@
           <t>gdmontero@caixabank.com</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6803,6 +8091,16 @@
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>profile: Barcelona, Spain (German Montero Mazza)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6831,7 +8129,7 @@
           <t>scedeno@caixabank.com</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6852,6 +8150,16 @@
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid; CaixaBank Design Lead</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6880,7 +8188,7 @@
           <t>avalls@caixabank.com</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6901,6 +8209,16 @@
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>profile: Barcelona, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6929,7 +8247,7 @@
           <t>emallart@caixabank.com</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6950,6 +8268,16 @@
         </is>
       </c>
       <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>profile: Barcelona Area, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6978,7 +8306,7 @@
           <t>jgaitx@caixabank.com</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -6999,6 +8327,16 @@
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Barcelona Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7027,7 +8365,7 @@
           <t>gbarnich@caixabank.com</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7048,6 +8386,16 @@
         </is>
       </c>
       <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>profile: Barcelona, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7076,7 +8424,7 @@
           <t>sergio.gutierrez.p@caixabank.com</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7097,6 +8445,16 @@
         </is>
       </c>
       <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain (Sergio Gutierrez Ponce)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7125,7 +8483,7 @@
           <t>rmorinm@caixabanktech.com</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7146,6 +8504,16 @@
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Madrid; CaixaBank Tech</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7174,7 +8542,7 @@
           <t>jguaus@caixabank.com</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7195,6 +8563,16 @@
         </is>
       </c>
       <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Barcelona Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7223,7 +8601,7 @@
           <t>cmanonelles@caixabankpc.com</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7244,6 +8622,16 @@
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>profile: Catalonia, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7272,7 +8660,7 @@
           <t>imolineroh@caixabank.com</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -7293,6 +8681,16 @@
         </is>
       </c>
       <c r="S138" s="2" t="inlineStr"/>
+      <c r="T138" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7321,7 +8719,7 @@
           <t>vladimir.kovtun@revolut.com</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7342,6 +8740,16 @@
         </is>
       </c>
       <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>no clean Revolut match; Revolut HQ (UK) default</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7370,7 +8778,7 @@
           <t>m.white@revolut.com</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7391,6 +8799,16 @@
         </is>
       </c>
       <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7419,7 +8837,7 @@
           <t>eleanor.taylor@revolut.com</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7440,6 +8858,16 @@
         </is>
       </c>
       <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>Revolut UK creative marketing; a Lisbon profile also exists - unconfirmed</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7468,7 +8896,7 @@
           <t>kuba.fast@revolut.com</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7489,6 +8917,16 @@
         </is>
       </c>
       <c r="S142" s="2" t="inlineStr"/>
+      <c r="T142" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>CEO Revolut Bank UAB (Vilnius, LITHUANIA entity); ex-Chase UK - physical base ambiguous UK/Lithuania - NEEDS REVIEW</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7517,7 +8955,7 @@
           <t>leila.sakhnini@revolut.com</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7538,6 +8976,16 @@
         </is>
       </c>
       <c r="S143" s="2" t="inlineStr"/>
+      <c r="T143" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/leilasakhnini</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -7566,7 +9014,7 @@
           <t>sofya.tretyakova@revolut.com</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7587,6 +9035,16 @@
         </is>
       </c>
       <c r="S144" s="2" t="inlineStr"/>
+      <c r="T144" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7615,9 +9073,9 @@
           <t>sonia.calderon@revolut.com</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -7636,6 +9094,16 @@
         </is>
       </c>
       <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>profile: Greater Barcelona Metropolitan Area (Sonia Rosales Calderon)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7664,9 +9132,9 @@
           <t>theau.guillot@revolut.com</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>France</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
@@ -7685,6 +9153,16 @@
         </is>
       </c>
       <c r="S146" s="2" t="inlineStr"/>
+      <c r="T146" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>profile: Paris; based remotely from France</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7713,9 +9191,9 @@
           <t>marco.tracogna@revolut.com</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -7734,6 +9212,16 @@
         </is>
       </c>
       <c r="S147" s="2" t="inlineStr"/>
+      <c r="T147" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>profile: Barcelona, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -7762,7 +9250,7 @@
           <t>sergey.puzin@revolut.com</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7783,6 +9271,16 @@
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr"/>
+      <c r="T148" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>no explicit location; Revolut HQ (UK) default</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -7811,9 +9309,9 @@
           <t>irina.zhukova@revolut.com</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
@@ -7832,6 +9330,16 @@
         </is>
       </c>
       <c r="S149" s="2" t="inlineStr"/>
+      <c r="T149" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>de.linkedin.com/in/irina-zhukova; ex-Freeletics (Munich)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -7860,7 +9368,7 @@
           <t>Edouard.daunizeau@revolut.com</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G150" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7881,6 +9389,16 @@
         </is>
       </c>
       <c r="S150" s="2" t="inlineStr"/>
+      <c r="T150" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB (South Hackney)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -7909,7 +9427,7 @@
           <t>wes.brannigan@revolut.com</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G151" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -7930,6 +9448,16 @@
         </is>
       </c>
       <c r="S151" s="2" t="inlineStr"/>
+      <c r="T151" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, England, UK; Head of Ops Revolut UK</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -7958,9 +9486,9 @@
           <t>Cedric.sevin@revolut.com</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7979,6 +9507,16 @@
         </is>
       </c>
       <c r="S152" s="2" t="inlineStr"/>
+      <c r="T152" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8007,9 +9545,9 @@
           <t>a.amorim@revolut.com</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -8028,6 +9566,16 @@
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr"/>
+      <c r="T153" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>pt.linkedin.com/in/afonsoamorimcoelho; Portugal (Revolut Porto)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8056,7 +9604,7 @@
           <t>pietro.dalpane@revolut.com</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8077,6 +9625,16 @@
         </is>
       </c>
       <c r="S154" s="2" t="inlineStr"/>
+      <c r="T154" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/pietro-dalpane; #londontech</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8105,7 +9663,7 @@
           <t>ziggy.pragier@wise.com</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G155" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8126,6 +9684,16 @@
         </is>
       </c>
       <c r="S155" s="2" t="inlineStr"/>
+      <c r="T155" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8154,7 +9722,7 @@
           <t>nilan.peiris@wise.com</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G156" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8175,6 +9743,16 @@
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8203,7 +9781,7 @@
           <t>josh.payton@wise.com</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G157" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8224,6 +9802,16 @@
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8252,7 +9840,7 @@
           <t>sonia.cialicu@wise.com</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8273,6 +9861,16 @@
         </is>
       </c>
       <c r="S158" s="2" t="inlineStr"/>
+      <c r="T158" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB; UK Companies House officer</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8301,7 +9899,7 @@
           <t>samuele.erbi@wise.com</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G159" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8322,6 +9920,16 @@
         </is>
       </c>
       <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8350,7 +9958,7 @@
           <t>magda.panfil@wise.com</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8371,6 +9979,16 @@
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; Wise HQ (UK) default (Wise also has Tallinn/Budapest hubs)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -8399,7 +10017,7 @@
           <t>ruth.chadwick@wise.com</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8420,6 +10038,16 @@
         </is>
       </c>
       <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -8448,7 +10076,7 @@
           <t>chetna.shastry@wise.com</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8469,6 +10097,16 @@
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -8497,7 +10135,7 @@
           <t>mike.shebalkov@wise.com</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8518,6 +10156,16 @@
         </is>
       </c>
       <c r="S163" s="2" t="inlineStr"/>
+      <c r="T163" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -8546,7 +10194,7 @@
           <t>ayesha.kadan@wise.com</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G164" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8567,6 +10215,16 @@
         </is>
       </c>
       <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin; ex-Uber Amsterdam - possibly NL, unconfirmed</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -8595,7 +10253,7 @@
           <t>samara.thomas@wise.com</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G165" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8616,6 +10274,16 @@
         </is>
       </c>
       <c r="S165" s="2" t="inlineStr"/>
+      <c r="T165" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/samaraschulz; Wise London</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -8644,7 +10312,7 @@
           <t>cian.weeresinghe@wise.com</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8665,6 +10333,16 @@
         </is>
       </c>
       <c r="S166" s="2" t="inlineStr"/>
+      <c r="T166" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, England, GB</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -8693,7 +10371,7 @@
           <t>alessandro.battaglia@wise.com</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8714,6 +10392,16 @@
         </is>
       </c>
       <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -8742,7 +10430,7 @@
           <t>Iona.carter@wise.com</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8763,6 +10451,16 @@
         </is>
       </c>
       <c r="S168" s="2" t="inlineStr"/>
+      <c r="T168" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/iona-carter; VP Brand Wise</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8791,7 +10489,7 @@
           <t>Natalie.malevsky@monzo.com</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8812,6 +10510,16 @@
         </is>
       </c>
       <c r="S169" s="2" t="inlineStr"/>
+      <c r="T169" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, England, GB</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8840,7 +10548,7 @@
           <t>nicolechristensen@monzo.com</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8861,6 +10569,16 @@
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr"/>
+      <c r="T170" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/nicolechris; Monzo EU expansion, UK-based</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -8889,7 +10607,7 @@
           <t>chrisnorell@monzo.com</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8910,6 +10628,16 @@
         </is>
       </c>
       <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -8938,7 +10666,7 @@
           <t>emilysuter@monzo.com</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -8959,6 +10687,16 @@
         </is>
       </c>
       <c r="S172" s="2" t="inlineStr"/>
+      <c r="T172" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin; Monzo London (Oxford grad)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -8987,7 +10725,7 @@
           <t>benlawrence@monzo.com</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9008,6 +10746,16 @@
         </is>
       </c>
       <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/benjlawrence; Monzo</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9036,7 +10784,7 @@
           <t>ranniepowell@monzo.com</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9057,6 +10805,16 @@
         </is>
       </c>
       <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>Monzo COO office (London); no explicit location</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -9085,7 +10843,7 @@
           <t>katiegormley@monzo.com</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9106,6 +10864,16 @@
         </is>
       </c>
       <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB (Katie Gormley)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9134,7 +10902,7 @@
           <t>karenaddy@monzo.com</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9155,6 +10923,16 @@
         </is>
       </c>
       <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/karen-addy; Monzo</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -9183,7 +10961,7 @@
           <t>arundhathidesai@monzo.com</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9204,6 +10982,16 @@
         </is>
       </c>
       <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -9232,7 +11020,7 @@
           <t>Rachad.khoury@monzo.com</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9253,6 +11041,16 @@
         </is>
       </c>
       <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -9281,7 +11079,7 @@
           <t>jordanshwide@monzo.com</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G179" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9302,6 +11100,16 @@
         </is>
       </c>
       <c r="S179" s="2" t="inlineStr"/>
+      <c r="T179" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9330,7 +11138,7 @@
           <t>katodonnell@monzo.com</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9351,6 +11159,16 @@
         </is>
       </c>
       <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, England, GB</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -9379,7 +11197,7 @@
           <t>Nicole.rudland@monzo.com</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9400,6 +11218,16 @@
         </is>
       </c>
       <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>Monzo Customer Ops (Cardiff/London/Remote UK); no explicit location</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -9428,7 +11256,7 @@
           <t>richharris@monzo.com</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9449,6 +11277,16 @@
         </is>
       </c>
       <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -9477,7 +11315,7 @@
           <t>shelleymalton@monzo.com</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9498,6 +11336,16 @@
         </is>
       </c>
       <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin; ex-NatWest, Monzo Group COO</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -9526,7 +11374,7 @@
           <t>jessie.harringtonbroome@starlingbank.com</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9547,6 +11395,16 @@
         </is>
       </c>
       <c r="S184" s="2" t="inlineStr"/>
+      <c r="T184" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom (Jessie Harrington Broome)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -9575,7 +11433,7 @@
           <t>joe.bakowski@starlingbank.com</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9596,6 +11454,16 @@
         </is>
       </c>
       <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>uk profile; ex-Metro Bank UK; Starling UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -9624,7 +11492,7 @@
           <t>chris.ross@starlingbank.com</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9645,6 +11513,16 @@
         </is>
       </c>
       <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>no clean match; Starling is UK-only</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -9673,7 +11551,7 @@
           <t>emma.stanning@starlingbank.com</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9694,6 +11572,16 @@
         </is>
       </c>
       <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U187" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -9722,7 +11610,7 @@
           <t>daniel.cosentino@starlingbank.com</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9743,6 +11631,16 @@
         </is>
       </c>
       <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -9771,7 +11669,7 @@
           <t>lisa.cunico@starlingbank.com</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9792,6 +11690,16 @@
         </is>
       </c>
       <c r="S189" s="2" t="inlineStr"/>
+      <c r="T189" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -9820,7 +11728,7 @@
           <t>michele.rousseau@starlingbank.com</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9841,6 +11749,16 @@
         </is>
       </c>
       <c r="S190" s="2" t="inlineStr"/>
+      <c r="T190" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>profile: United Kingdom; Starling CMO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -9869,7 +11787,7 @@
           <t>raghu.narula@starlingbank.com</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9890,6 +11808,16 @@
         </is>
       </c>
       <c r="S191" s="2" t="inlineStr"/>
+      <c r="T191" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>ex-NatWest UK; Starling is UK-only; no explicit location</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -9918,7 +11846,7 @@
           <t>indiana.matine@starlingbank.com</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9939,6 +11867,16 @@
         </is>
       </c>
       <c r="S192" s="2" t="inlineStr"/>
+      <c r="T192" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -9967,7 +11905,7 @@
           <t>luke.farrell@starlingbank.com</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -9988,6 +11926,16 @@
         </is>
       </c>
       <c r="S193" s="2" t="inlineStr"/>
+      <c r="T193" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr">
+        <is>
+          <t>profile: London</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10016,7 +11964,7 @@
           <t>evangelos.rakovitis@starlingbank.com</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -10037,6 +11985,16 @@
         </is>
       </c>
       <c r="S194" s="2" t="inlineStr"/>
+      <c r="T194" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>profile: London, GB</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10065,7 +12023,7 @@
           <t>sami.kade@starlingbank.com</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -10086,6 +12044,16 @@
         </is>
       </c>
       <c r="S195" s="2" t="inlineStr"/>
+      <c r="T195" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>Starling UK-only; no explicit location on profile</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10114,7 +12082,7 @@
           <t>aaron.shaw@starlingbank.com</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
@@ -10135,6 +12103,16 @@
         </is>
       </c>
       <c r="S196" s="2" t="inlineStr"/>
+      <c r="T196" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/aarshaw; Starling</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10163,7 +12141,7 @@
           <t>luis.franqueira@n26.com</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10184,6 +12162,16 @@
         </is>
       </c>
       <c r="S197" s="2" t="inlineStr"/>
+      <c r="T197" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -10212,7 +12200,7 @@
           <t>prithvi.sarkar@n26.com</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10233,6 +12221,16 @@
         </is>
       </c>
       <c r="S198" s="2" t="inlineStr"/>
+      <c r="T198" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -10261,9 +12259,9 @@
           <t>catalina.garcia@n26.com</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
@@ -10282,6 +12280,16 @@
         </is>
       </c>
       <c r="S199" s="2" t="inlineStr"/>
+      <c r="T199" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>profile: Madrid, Spain; N26 Iberia marketing</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10310,7 +12318,7 @@
           <t>covadonga.garcia@n26.com</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G200" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10331,6 +12339,16 @@
         </is>
       </c>
       <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>profile: Berlin, DE</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -10359,7 +12377,7 @@
           <t>laura.cristaldi@n26.com</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10380,6 +12398,16 @@
         </is>
       </c>
       <c r="S201" s="2" t="inlineStr"/>
+      <c r="T201" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>profile: Berlin Metropolitan Area</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -10408,7 +12436,7 @@
           <t>niklas.oertel@n26.com</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10429,6 +12457,16 @@
         </is>
       </c>
       <c r="S202" s="2" t="inlineStr"/>
+      <c r="T202" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); title 'Head of Growth - Germany' -&gt; Germany</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -10453,7 +12491,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10474,6 +12512,16 @@
         </is>
       </c>
       <c r="S203" s="2" t="inlineStr"/>
+      <c r="T203" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U203" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); no email; N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -10502,7 +12550,7 @@
           <t>will.sorber@n26.com</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10523,6 +12571,16 @@
         </is>
       </c>
       <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -10551,7 +12609,7 @@
           <t>katharina.pollak@n26.com</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G205" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10572,6 +12630,16 @@
         </is>
       </c>
       <c r="S205" s="2" t="inlineStr"/>
+      <c r="T205" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>de.linkedin.com/in/katharina-pollak; N26 (Berlin)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -10600,7 +12668,7 @@
           <t>crystal.goh@n26.com</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10621,6 +12689,16 @@
         </is>
       </c>
       <c r="S206" s="2" t="inlineStr"/>
+      <c r="T206" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -10649,7 +12727,7 @@
           <t>holger.boehmer@n26.com</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10670,6 +12748,16 @@
         </is>
       </c>
       <c r="S207" s="2" t="inlineStr"/>
+      <c r="T207" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); MD N26 Operations GmbH -&gt; Germany</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -10698,7 +12786,7 @@
           <t>siddharth.paul@n26.com</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10719,6 +12807,16 @@
         </is>
       </c>
       <c r="S208" s="2" t="inlineStr"/>
+      <c r="T208" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -10747,7 +12845,7 @@
           <t>christopher.poots@n26.com</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10768,6 +12866,16 @@
         </is>
       </c>
       <c r="S209" s="2" t="inlineStr"/>
+      <c r="T209" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); N26 Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -10796,7 +12904,7 @@
           <t>marcus.letsch@traderepublic.com</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10817,6 +12925,16 @@
         </is>
       </c>
       <c r="S210" s="2" t="inlineStr"/>
+      <c r="T210" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -10845,7 +12963,7 @@
           <t>nina.jetter@traderepublic.com</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10866,6 +12984,16 @@
         </is>
       </c>
       <c r="S211" s="2" t="inlineStr"/>
+      <c r="T211" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U211" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -10894,7 +13022,7 @@
           <t>alexander.blum@traderepublic.com</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G212" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10915,6 +13043,16 @@
         </is>
       </c>
       <c r="S212" s="2" t="inlineStr"/>
+      <c r="T212" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U212" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -10943,7 +13081,7 @@
           <t>julian.collin@traderepublic.com</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -10964,6 +13102,16 @@
         </is>
       </c>
       <c r="S213" s="2" t="inlineStr"/>
+      <c r="T213" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); 'GM International Markets' - HQ default, may differ</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -10992,7 +13140,7 @@
           <t>ulrich.schroeer@traderepublic.com</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G214" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11013,6 +13161,16 @@
         </is>
       </c>
       <c r="S214" s="2" t="inlineStr"/>
+      <c r="T214" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11041,7 +13199,7 @@
           <t>daniel.montero@traderepublic.com</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G215" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11062,6 +13220,16 @@
         </is>
       </c>
       <c r="S215" s="2" t="inlineStr"/>
+      <c r="T215" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11090,7 +13258,7 @@
           <t>Kirill.novikov@traderepublic.com</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G216" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11111,6 +13279,16 @@
         </is>
       </c>
       <c r="S216" s="2" t="inlineStr"/>
+      <c r="T216" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11139,7 +13317,7 @@
           <t>ghazal.azari@traderepublic.com</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G217" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11160,6 +13338,16 @@
         </is>
       </c>
       <c r="S217" s="2" t="inlineStr"/>
+      <c r="T217" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11188,7 +13376,7 @@
           <t>Dora.trostanetsky@traderepublic.com</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G218" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11209,6 +13397,16 @@
         </is>
       </c>
       <c r="S218" s="2" t="inlineStr"/>
+      <c r="T218" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U218" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -11237,7 +13435,7 @@
           <t>felix.jamestin@traderepublic.com</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G219" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11258,6 +13456,16 @@
         </is>
       </c>
       <c r="S219" s="2" t="inlineStr"/>
+      <c r="T219" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U219" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -11286,7 +13494,7 @@
           <t>laura.eggers@traderepublic.com</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G220" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11307,6 +13515,16 @@
         </is>
       </c>
       <c r="S220" s="2" t="inlineStr"/>
+      <c r="T220" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U220" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -11335,7 +13553,7 @@
           <t>victor.kovatsenko@traderepublic.com</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G221" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
@@ -11356,9 +13574,19 @@
         </is>
       </c>
       <c r="S221" s="2" t="inlineStr"/>
+      <c r="T221" s="3" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="U221" s="2" t="inlineStr">
+        <is>
+          <t>not searched (search cap); TR Berlin HQ default</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S221"/>
+  <autoFilter ref="A1:U221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11369,173 +13597,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>London Finance Conference - Prospecting List</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
+      <c r="A2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total contacts: 220   |   Companies: 20</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Format: matches your CRM import template (columns A-S).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
+      <c r="A5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Columns populated from the source list:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - First Name, Last Name  (split from the full name)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Job Title</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Company</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Email</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Country  (pre-filled from each company's HQ country - please verify per contact)</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Country  (LinkedIn/web cross-reference - see Country Confidence)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Vertical  (set to 'Financial Services' for all rows)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Country column - how it was determined:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Each contact's name + title + company was searched on the web to find their</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  matching LinkedIn profile, then the profile's location was used for Country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Two helper columns (T and U, OUTSIDE the A-S import range) record this:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Country Confidence:  'Verified' (green) = a matching profile showed a real</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      location signal (explicit city/country or a country-coded LinkedIn subdomain);</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      'Assumed' (orange) = no confident match, fell back to the company HQ country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Country Evidence:  the specific signal used for each row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOTE: remove columns T and U before importing if your CRM expects only A-S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  All countries fall within your 6: UK, France, Germany, Netherlands, Spain, Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXCEPTIONS found outside those 6 (please review - see orange/notes):</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Walter Rizzi &amp; Nicola Cecchetto (BBVA) -&gt; Italy (Milan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Martin Eizaga (BBVA) -&gt; Italy (likely; BBVA Digital Banking Italy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Kuba Fast (Revolut) -&gt; CEO of Revolut's Lithuania entity (Vilnius); ex-Chase UK,</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      physical base ambiguous UK/Lithuania - marked UK/Assumed, NEEDS REVIEW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ~21 contacts (rest of N26 + all Trade Republic) could not be searched (hit the</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  session's 200-search limit); they use the Berlin/Germany HQ default (Assumed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Columns intentionally left blank for the marketing team to complete</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>(these depend on your CRM picklists / campaign setup):</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phone, State (US), Source, Lead Status, Privacy Policy Accepted, Score,</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Owner email address, Lead Queue, Main Marketing Language, Lead Type 1,</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lead Sub Type, Brand Preference</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Notes on the data:</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Two contacts had no email in the source (Lisa Barahona / Deutsche Bank,</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">    Pierre Plessis / N26); their Email cells are blank.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - One source email had a typo (kuba,fast@revolut.com) - corrected to</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">    kuba.fast@revolut.com. Please confirm before sending.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Accented characters in some French/Portuguese titles were simplified to</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">    plain ASCII for clean CRM import.</t>
         </is>
